--- a/tables/svm_per_anomaly_type_metrics.xlsx
+++ b/tables/svm_per_anomaly_type_metrics.xlsx
@@ -453,14 +453,14 @@
         <v>627</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.014</t>
         </is>
       </c>
     </row>
@@ -474,14 +474,14 @@
         <v>620</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.015</t>
         </is>
       </c>
     </row>

--- a/tables/svm_per_anomaly_type_metrics.xlsx
+++ b/tables/svm_per_anomaly_type_metrics.xlsx
@@ -453,14 +453,14 @@
         <v>627</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.006</t>
         </is>
       </c>
     </row>
@@ -474,14 +474,14 @@
         <v>620</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.008</t>
         </is>
       </c>
     </row>

--- a/tables/svm_per_anomaly_type_metrics.xlsx
+++ b/tables/svm_per_anomaly_type_metrics.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Anomaly Type</t>
+          <t>Anomalietyp</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Anzahl</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
